--- a/src/main/resources/FeatureFiles/.done/ContactUsPage_Firefox.xlsx
+++ b/src/main/resources/FeatureFiles/.done/ContactUsPage_Firefox.xlsx
@@ -294,7 +294,7 @@
     <t>firefox</t>
   </si>
   <si>
-    <t>openBrowser</t>
+    <t>openHeadlessBrowser</t>
   </si>
 </sst>
 </file>
